--- a/public/plantilla-incidente-ambiental.xlsx
+++ b/public/plantilla-incidente-ambiental.xlsx
@@ -15,6 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="hh:mm"/>
+  </numFmts>
   <fonts count="20">
     <font>
       <name val="Calibri"/>
@@ -554,19 +557,19 @@
     <xf numFmtId="4" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -615,7 +618,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -668,7 +671,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">

--- a/public/plantilla-incidente-ambiental.xlsx
+++ b/public/plantilla-incidente-ambiental.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="9" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incidente Ambiental" sheetId="1" state="visible" r:id="rId1"/>

--- a/public/plantilla-incidente-ambiental.xlsx
+++ b/public/plantilla-incidente-ambiental.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incidente Ambiental" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,9 +16,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="hh:mm"/>
+    <numFmt numFmtId="164" formatCode="hh:mm"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -163,6 +163,10 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="17">
     <fill>
@@ -529,7 +533,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -560,7 +564,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -636,7 +640,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -757,6 +761,56 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1219,6 +1273,7 @@
   <cols>
     <col width="12.77734375" customWidth="1" style="27" min="1" max="1"/>
     <col width="13" customWidth="1" style="27" min="2" max="3"/>
+    <col width="13" customWidth="1" style="27" min="3" max="3"/>
     <col width="15.77734375" customWidth="1" style="27" min="4" max="4"/>
     <col width="10" customWidth="1" style="27" min="5" max="5"/>
     <col width="15.77734375" customWidth="1" style="27" min="6" max="6"/>
@@ -1386,20 +1441,20 @@
         </is>
       </c>
       <c r="B11" s="22" t="n"/>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="25" t="n"/>
-      <c r="E11" s="25" t="n"/>
-      <c r="F11" s="25" t="n"/>
-      <c r="G11" s="22" t="n"/>
+      <c r="C11" s="97" t="n"/>
+      <c r="D11" s="98" t="n"/>
+      <c r="E11" s="98" t="n"/>
+      <c r="F11" s="98" t="n"/>
+      <c r="G11" s="99" t="n"/>
       <c r="H11" s="88" t="inlineStr">
         <is>
           <t>Reporte N°</t>
         </is>
       </c>
       <c r="I11" s="22" t="n"/>
-      <c r="J11" s="32" t="n"/>
-      <c r="K11" s="25" t="n"/>
-      <c r="L11" s="22" t="n"/>
+      <c r="J11" s="100" t="n"/>
+      <c r="K11" s="98" t="n"/>
+      <c r="L11" s="99" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="27">
       <c r="A12" s="88" t="inlineStr">
@@ -1408,20 +1463,20 @@
         </is>
       </c>
       <c r="B12" s="22" t="n"/>
-      <c r="C12" s="24" t="n"/>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="25" t="n"/>
-      <c r="F12" s="25" t="n"/>
-      <c r="G12" s="22" t="n"/>
+      <c r="C12" s="97" t="n"/>
+      <c r="D12" s="98" t="n"/>
+      <c r="E12" s="98" t="n"/>
+      <c r="F12" s="98" t="n"/>
+      <c r="G12" s="99" t="n"/>
       <c r="H12" s="88" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
       <c r="I12" s="22" t="n"/>
-      <c r="J12" s="24" t="n"/>
-      <c r="K12" s="25" t="n"/>
-      <c r="L12" s="22" t="n"/>
+      <c r="J12" s="97" t="n"/>
+      <c r="K12" s="98" t="n"/>
+      <c r="L12" s="99" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="27">
       <c r="A13" s="88" t="inlineStr">
@@ -1430,24 +1485,24 @@
         </is>
       </c>
       <c r="B13" s="22" t="n"/>
-      <c r="C13" s="23" t="n"/>
-      <c r="D13" s="22" t="n"/>
+      <c r="C13" s="101" t="n"/>
+      <c r="D13" s="99" t="n"/>
       <c r="E13" s="88" t="inlineStr">
         <is>
           <t>Hora del evento</t>
         </is>
       </c>
       <c r="F13" s="22" t="n"/>
-      <c r="G13" s="44" t="n"/>
-      <c r="H13" s="22" t="n"/>
+      <c r="G13" s="102" t="n"/>
+      <c r="H13" s="99" t="n"/>
       <c r="I13" s="88" t="inlineStr">
         <is>
           <t>Hora del reporte</t>
         </is>
       </c>
       <c r="J13" s="22" t="n"/>
-      <c r="K13" s="44" t="n"/>
-      <c r="L13" s="22" t="n"/>
+      <c r="K13" s="102" t="n"/>
+      <c r="L13" s="99" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1" s="27">
       <c r="A14" s="88" t="inlineStr">
@@ -1456,20 +1511,20 @@
         </is>
       </c>
       <c r="B14" s="22" t="n"/>
-      <c r="C14" s="24" t="n"/>
-      <c r="D14" s="25" t="n"/>
-      <c r="E14" s="25" t="n"/>
-      <c r="F14" s="25" t="n"/>
-      <c r="G14" s="22" t="n"/>
+      <c r="C14" s="97" t="n"/>
+      <c r="D14" s="98" t="n"/>
+      <c r="E14" s="98" t="n"/>
+      <c r="F14" s="98" t="n"/>
+      <c r="G14" s="99" t="n"/>
       <c r="H14" s="88" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
       <c r="I14" s="22" t="n"/>
-      <c r="J14" s="24" t="n"/>
-      <c r="K14" s="25" t="n"/>
-      <c r="L14" s="22" t="n"/>
+      <c r="J14" s="97" t="n"/>
+      <c r="K14" s="98" t="n"/>
+      <c r="L14" s="99" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1" s="27">
       <c r="A15" s="88" t="inlineStr">
@@ -1478,20 +1533,20 @@
         </is>
       </c>
       <c r="B15" s="22" t="n"/>
-      <c r="C15" s="24" t="n"/>
-      <c r="D15" s="25" t="n"/>
-      <c r="E15" s="25" t="n"/>
-      <c r="F15" s="25" t="n"/>
-      <c r="G15" s="22" t="n"/>
+      <c r="C15" s="97" t="n"/>
+      <c r="D15" s="98" t="n"/>
+      <c r="E15" s="98" t="n"/>
+      <c r="F15" s="98" t="n"/>
+      <c r="G15" s="99" t="n"/>
       <c r="H15" s="88" t="inlineStr">
         <is>
           <t>Coordenadas</t>
         </is>
       </c>
       <c r="I15" s="22" t="n"/>
-      <c r="J15" s="32" t="n"/>
-      <c r="K15" s="25" t="n"/>
-      <c r="L15" s="22" t="n"/>
+      <c r="J15" s="100" t="n"/>
+      <c r="K15" s="98" t="n"/>
+      <c r="L15" s="99" t="n"/>
     </row>
     <row r="16" ht="16.5" customHeight="1" s="27">
       <c r="A16" s="77" t="inlineStr">
@@ -1512,7 +1567,7 @@
       <c r="L16" s="18" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1" s="27">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="103" t="inlineStr">
         <is>
           <t>☐ Derrame de combustible o aceite</t>
         </is>
@@ -1520,7 +1575,7 @@
       <c r="B17" s="17" t="n"/>
       <c r="C17" s="17" t="n"/>
       <c r="D17" s="18" t="n"/>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="103" t="inlineStr">
         <is>
           <t>☐ Vertimiento no controlado</t>
         </is>
@@ -1528,7 +1583,7 @@
       <c r="F17" s="17" t="n"/>
       <c r="G17" s="17" t="n"/>
       <c r="H17" s="18" t="n"/>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I17" s="103" t="inlineStr">
         <is>
           <t>☐ Emisión de polvo o gases</t>
         </is>
@@ -1538,7 +1593,7 @@
       <c r="L17" s="18" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1" s="27">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="103" t="inlineStr">
         <is>
           <t>☐ Incendio con afectación ambiental</t>
         </is>
@@ -1546,7 +1601,7 @@
       <c r="B18" s="17" t="n"/>
       <c r="C18" s="17" t="n"/>
       <c r="D18" s="18" t="n"/>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E18" s="103" t="inlineStr">
         <is>
           <t>☐ Afectación a fauna o flora</t>
         </is>
@@ -1554,7 +1609,7 @@
       <c r="F18" s="17" t="n"/>
       <c r="G18" s="17" t="n"/>
       <c r="H18" s="18" t="n"/>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="I18" s="103" t="inlineStr">
         <is>
           <t>☐ Afectación a un cuerpo de agua</t>
         </is>
@@ -1564,7 +1619,7 @@
       <c r="L18" s="18" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1" s="27">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="103" t="inlineStr">
         <is>
           <t>☐ Residuos mal dispuestos</t>
         </is>
@@ -1572,7 +1627,7 @@
       <c r="B19" s="17" t="n"/>
       <c r="C19" s="17" t="n"/>
       <c r="D19" s="18" t="n"/>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="103" t="inlineStr">
         <is>
           <t>☐ Daño a redes o servicios</t>
         </is>
@@ -1580,7 +1635,7 @@
       <c r="F19" s="17" t="n"/>
       <c r="G19" s="17" t="n"/>
       <c r="H19" s="18" t="n"/>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="I19" s="103" t="inlineStr">
         <is>
           <t>☐ Ruido o vibración fuera de norma</t>
         </is>
@@ -1590,7 +1645,7 @@
       <c r="L19" s="18" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1" s="27">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="103" t="inlineStr">
         <is>
           <t>☐ Otro:</t>
         </is>
@@ -1624,16 +1679,16 @@
         </is>
       </c>
       <c r="B22" s="22" t="n"/>
-      <c r="C22" s="40" t="n"/>
-      <c r="D22" s="25" t="n"/>
-      <c r="E22" s="25" t="n"/>
-      <c r="F22" s="25" t="n"/>
-      <c r="G22" s="25" t="n"/>
-      <c r="H22" s="25" t="n"/>
-      <c r="I22" s="25" t="n"/>
-      <c r="J22" s="25" t="n"/>
-      <c r="K22" s="25" t="n"/>
-      <c r="L22" s="22" t="n"/>
+      <c r="C22" s="104" t="n"/>
+      <c r="D22" s="98" t="n"/>
+      <c r="E22" s="98" t="n"/>
+      <c r="F22" s="98" t="n"/>
+      <c r="G22" s="98" t="n"/>
+      <c r="H22" s="98" t="n"/>
+      <c r="I22" s="98" t="n"/>
+      <c r="J22" s="98" t="n"/>
+      <c r="K22" s="98" t="n"/>
+      <c r="L22" s="99" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1" s="27">
       <c r="A23" s="88" t="inlineStr">
@@ -1642,16 +1697,16 @@
         </is>
       </c>
       <c r="B23" s="22" t="n"/>
-      <c r="C23" s="40" t="n"/>
-      <c r="D23" s="25" t="n"/>
-      <c r="E23" s="25" t="n"/>
-      <c r="F23" s="25" t="n"/>
-      <c r="G23" s="25" t="n"/>
-      <c r="H23" s="25" t="n"/>
-      <c r="I23" s="25" t="n"/>
-      <c r="J23" s="25" t="n"/>
-      <c r="K23" s="25" t="n"/>
-      <c r="L23" s="22" t="n"/>
+      <c r="C23" s="104" t="n"/>
+      <c r="D23" s="98" t="n"/>
+      <c r="E23" s="98" t="n"/>
+      <c r="F23" s="98" t="n"/>
+      <c r="G23" s="98" t="n"/>
+      <c r="H23" s="98" t="n"/>
+      <c r="I23" s="98" t="n"/>
+      <c r="J23" s="98" t="n"/>
+      <c r="K23" s="98" t="n"/>
+      <c r="L23" s="99" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1" s="27">
       <c r="A24" s="88" t="inlineStr">
@@ -1660,20 +1715,20 @@
         </is>
       </c>
       <c r="B24" s="22" t="n"/>
-      <c r="C24" s="24" t="n"/>
-      <c r="D24" s="25" t="n"/>
-      <c r="E24" s="25" t="n"/>
-      <c r="F24" s="25" t="n"/>
-      <c r="G24" s="22" t="n"/>
+      <c r="C24" s="97" t="n"/>
+      <c r="D24" s="98" t="n"/>
+      <c r="E24" s="98" t="n"/>
+      <c r="F24" s="98" t="n"/>
+      <c r="G24" s="99" t="n"/>
       <c r="H24" s="88" t="inlineStr">
         <is>
           <t>Cantidad estimada</t>
         </is>
       </c>
       <c r="I24" s="22" t="n"/>
-      <c r="J24" s="32" t="n"/>
-      <c r="K24" s="25" t="n"/>
-      <c r="L24" s="22" t="n"/>
+      <c r="J24" s="100" t="n"/>
+      <c r="K24" s="98" t="n"/>
+      <c r="L24" s="99" t="n"/>
     </row>
     <row r="25" ht="16.5" customHeight="1" s="27">
       <c r="A25" s="77" t="inlineStr">
@@ -1694,28 +1749,28 @@
       <c r="L25" s="18" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1" s="27">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="103" t="inlineStr">
         <is>
           <t>☐ Suelo</t>
         </is>
       </c>
       <c r="B26" s="17" t="n"/>
       <c r="C26" s="18" t="n"/>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D26" s="103" t="inlineStr">
         <is>
           <t>☐ Agua superficial o subterránea</t>
         </is>
       </c>
       <c r="E26" s="17" t="n"/>
       <c r="F26" s="18" t="n"/>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="G26" s="103" t="inlineStr">
         <is>
           <t>☐ Aire</t>
         </is>
       </c>
       <c r="H26" s="17" t="n"/>
       <c r="I26" s="18" t="n"/>
-      <c r="J26" s="16" t="inlineStr">
+      <c r="J26" s="103" t="inlineStr">
         <is>
           <t>☐ Flora</t>
         </is>
@@ -1724,28 +1779,28 @@
       <c r="L26" s="18" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1" s="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="103" t="inlineStr">
         <is>
           <t>☐ Fauna</t>
         </is>
       </c>
       <c r="B27" s="17" t="n"/>
       <c r="C27" s="18" t="n"/>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D27" s="103" t="inlineStr">
         <is>
           <t>☐ Comunidad</t>
         </is>
       </c>
       <c r="E27" s="17" t="n"/>
       <c r="F27" s="18" t="n"/>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G27" s="103" t="inlineStr">
         <is>
           <t>☐ Infraestructura</t>
         </is>
       </c>
       <c r="H27" s="17" t="n"/>
       <c r="I27" s="18" t="n"/>
-      <c r="J27" s="16" t="inlineStr">
+      <c r="J27" s="103" t="inlineStr">
         <is>
           <t>☐ Sin afectación</t>
         </is>
@@ -1760,24 +1815,24 @@
         </is>
       </c>
       <c r="B28" s="22" t="n"/>
-      <c r="C28" s="32" t="n"/>
-      <c r="D28" s="22" t="n"/>
+      <c r="C28" s="100" t="n"/>
+      <c r="D28" s="99" t="n"/>
       <c r="E28" s="88" t="inlineStr">
         <is>
           <t>Personas afectadas</t>
         </is>
       </c>
       <c r="F28" s="22" t="n"/>
-      <c r="G28" s="32" t="n"/>
-      <c r="H28" s="22" t="n"/>
+      <c r="G28" s="100" t="n"/>
+      <c r="H28" s="99" t="n"/>
       <c r="I28" s="88" t="inlineStr">
         <is>
           <t>Área afectada (m²)</t>
         </is>
       </c>
       <c r="J28" s="22" t="n"/>
-      <c r="K28" s="32" t="n"/>
-      <c r="L28" s="22" t="n"/>
+      <c r="K28" s="100" t="n"/>
+      <c r="L28" s="99" t="n"/>
     </row>
     <row r="29" ht="21" customHeight="1" s="27">
       <c r="A29" s="88" t="inlineStr">
@@ -1786,24 +1841,24 @@
         </is>
       </c>
       <c r="B29" s="22" t="n"/>
-      <c r="C29" s="32" t="n"/>
-      <c r="D29" s="22" t="n"/>
+      <c r="C29" s="100" t="n"/>
+      <c r="D29" s="99" t="n"/>
       <c r="E29" s="88" t="inlineStr">
         <is>
           <t>Autoridad</t>
         </is>
       </c>
       <c r="F29" s="22" t="n"/>
-      <c r="G29" s="24" t="n"/>
-      <c r="H29" s="22" t="n"/>
+      <c r="G29" s="97" t="n"/>
+      <c r="H29" s="99" t="n"/>
       <c r="I29" s="88" t="inlineStr">
         <is>
           <t>Fecha y radicado</t>
         </is>
       </c>
       <c r="J29" s="22" t="n"/>
-      <c r="K29" s="24" t="n"/>
-      <c r="L29" s="22" t="n"/>
+      <c r="K29" s="97" t="n"/>
+      <c r="L29" s="99" t="n"/>
     </row>
     <row r="30" ht="16.5" customHeight="1" s="27">
       <c r="A30" s="77" t="inlineStr">
@@ -1830,16 +1885,16 @@
         </is>
       </c>
       <c r="B31" s="22" t="n"/>
-      <c r="C31" s="40" t="n"/>
-      <c r="D31" s="25" t="n"/>
-      <c r="E31" s="25" t="n"/>
-      <c r="F31" s="25" t="n"/>
-      <c r="G31" s="25" t="n"/>
-      <c r="H31" s="25" t="n"/>
-      <c r="I31" s="25" t="n"/>
-      <c r="J31" s="25" t="n"/>
-      <c r="K31" s="25" t="n"/>
-      <c r="L31" s="22" t="n"/>
+      <c r="C31" s="104" t="n"/>
+      <c r="D31" s="98" t="n"/>
+      <c r="E31" s="98" t="n"/>
+      <c r="F31" s="98" t="n"/>
+      <c r="G31" s="98" t="n"/>
+      <c r="H31" s="98" t="n"/>
+      <c r="I31" s="98" t="n"/>
+      <c r="J31" s="98" t="n"/>
+      <c r="K31" s="98" t="n"/>
+      <c r="L31" s="99" t="n"/>
     </row>
     <row r="32" ht="21" customHeight="1" s="27">
       <c r="A32" s="88" t="inlineStr">
@@ -1848,20 +1903,20 @@
         </is>
       </c>
       <c r="B32" s="22" t="n"/>
-      <c r="C32" s="24" t="n"/>
-      <c r="D32" s="25" t="n"/>
-      <c r="E32" s="25" t="n"/>
-      <c r="F32" s="25" t="n"/>
-      <c r="G32" s="22" t="n"/>
+      <c r="C32" s="97" t="n"/>
+      <c r="D32" s="98" t="n"/>
+      <c r="E32" s="98" t="n"/>
+      <c r="F32" s="98" t="n"/>
+      <c r="G32" s="99" t="n"/>
       <c r="H32" s="88" t="inlineStr">
         <is>
           <t>Disposición final</t>
         </is>
       </c>
       <c r="I32" s="22" t="n"/>
-      <c r="J32" s="24" t="n"/>
-      <c r="K32" s="25" t="n"/>
-      <c r="L32" s="22" t="n"/>
+      <c r="J32" s="97" t="n"/>
+      <c r="K32" s="98" t="n"/>
+      <c r="L32" s="99" t="n"/>
     </row>
     <row r="33" ht="16.5" customHeight="1" s="27">
       <c r="A33" s="77" t="inlineStr">
@@ -1888,16 +1943,16 @@
         </is>
       </c>
       <c r="B34" s="22" t="n"/>
-      <c r="C34" s="40" t="n"/>
-      <c r="D34" s="25" t="n"/>
-      <c r="E34" s="25" t="n"/>
-      <c r="F34" s="25" t="n"/>
-      <c r="G34" s="25" t="n"/>
-      <c r="H34" s="25" t="n"/>
-      <c r="I34" s="25" t="n"/>
-      <c r="J34" s="25" t="n"/>
-      <c r="K34" s="25" t="n"/>
-      <c r="L34" s="22" t="n"/>
+      <c r="C34" s="104" t="n"/>
+      <c r="D34" s="98" t="n"/>
+      <c r="E34" s="98" t="n"/>
+      <c r="F34" s="98" t="n"/>
+      <c r="G34" s="98" t="n"/>
+      <c r="H34" s="98" t="n"/>
+      <c r="I34" s="98" t="n"/>
+      <c r="J34" s="98" t="n"/>
+      <c r="K34" s="98" t="n"/>
+      <c r="L34" s="99" t="n"/>
     </row>
     <row r="35" ht="22.05" customHeight="1" s="27">
       <c r="A35" s="80" t="inlineStr">
@@ -1934,52 +1989,52 @@
       </c>
     </row>
     <row r="36" ht="24" customHeight="1" s="27">
-      <c r="A36" s="41" t="n">
+      <c r="A36" s="105" t="n">
         <v>1</v>
       </c>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="17" t="n"/>
-      <c r="D36" s="17" t="n"/>
-      <c r="E36" s="17" t="n"/>
-      <c r="F36" s="18" t="n"/>
-      <c r="G36" s="16" t="n"/>
-      <c r="H36" s="17" t="n"/>
-      <c r="I36" s="18" t="n"/>
-      <c r="J36" s="26" t="n"/>
-      <c r="K36" s="18" t="n"/>
-      <c r="L36" s="41" t="n"/>
+      <c r="B36" s="106" t="n"/>
+      <c r="C36" s="107" t="n"/>
+      <c r="D36" s="107" t="n"/>
+      <c r="E36" s="107" t="n"/>
+      <c r="F36" s="108" t="n"/>
+      <c r="G36" s="106" t="n"/>
+      <c r="H36" s="107" t="n"/>
+      <c r="I36" s="108" t="n"/>
+      <c r="J36" s="109" t="n"/>
+      <c r="K36" s="108" t="n"/>
+      <c r="L36" s="110" t="n"/>
     </row>
     <row r="37" ht="24" customHeight="1" s="27">
-      <c r="A37" s="41" t="n">
+      <c r="A37" s="105" t="n">
         <v>2</v>
       </c>
-      <c r="B37" s="16" t="n"/>
-      <c r="C37" s="17" t="n"/>
-      <c r="D37" s="17" t="n"/>
-      <c r="E37" s="17" t="n"/>
-      <c r="F37" s="18" t="n"/>
-      <c r="G37" s="16" t="n"/>
-      <c r="H37" s="17" t="n"/>
-      <c r="I37" s="18" t="n"/>
-      <c r="J37" s="26" t="n"/>
-      <c r="K37" s="18" t="n"/>
-      <c r="L37" s="41" t="n"/>
+      <c r="B37" s="106" t="n"/>
+      <c r="C37" s="107" t="n"/>
+      <c r="D37" s="107" t="n"/>
+      <c r="E37" s="107" t="n"/>
+      <c r="F37" s="108" t="n"/>
+      <c r="G37" s="106" t="n"/>
+      <c r="H37" s="107" t="n"/>
+      <c r="I37" s="108" t="n"/>
+      <c r="J37" s="109" t="n"/>
+      <c r="K37" s="108" t="n"/>
+      <c r="L37" s="110" t="n"/>
     </row>
     <row r="38" ht="24" customHeight="1" s="27">
-      <c r="A38" s="41" t="n">
+      <c r="A38" s="105" t="n">
         <v>3</v>
       </c>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="17" t="n"/>
-      <c r="D38" s="17" t="n"/>
-      <c r="E38" s="17" t="n"/>
-      <c r="F38" s="18" t="n"/>
-      <c r="G38" s="16" t="n"/>
-      <c r="H38" s="17" t="n"/>
-      <c r="I38" s="18" t="n"/>
-      <c r="J38" s="26" t="n"/>
-      <c r="K38" s="18" t="n"/>
-      <c r="L38" s="41" t="n"/>
+      <c r="B38" s="106" t="n"/>
+      <c r="C38" s="107" t="n"/>
+      <c r="D38" s="107" t="n"/>
+      <c r="E38" s="107" t="n"/>
+      <c r="F38" s="108" t="n"/>
+      <c r="G38" s="106" t="n"/>
+      <c r="H38" s="107" t="n"/>
+      <c r="I38" s="108" t="n"/>
+      <c r="J38" s="109" t="n"/>
+      <c r="K38" s="108" t="n"/>
+      <c r="L38" s="110" t="n"/>
     </row>
     <row r="39" ht="16.5" customHeight="1" s="27">
       <c r="A39" s="77" t="inlineStr">
@@ -2006,24 +2061,24 @@
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
-      <c r="C40" s="32" t="n"/>
-      <c r="D40" s="22" t="n"/>
+      <c r="C40" s="100" t="n"/>
+      <c r="D40" s="99" t="n"/>
       <c r="E40" s="88" t="inlineStr">
         <is>
           <t>Fecha de cierre</t>
         </is>
       </c>
       <c r="F40" s="22" t="n"/>
-      <c r="G40" s="23" t="n"/>
-      <c r="H40" s="22" t="n"/>
+      <c r="G40" s="101" t="n"/>
+      <c r="H40" s="99" t="n"/>
       <c r="I40" s="88" t="inlineStr">
         <is>
           <t>Verificó el cierre</t>
         </is>
       </c>
       <c r="J40" s="22" t="n"/>
-      <c r="K40" s="24" t="n"/>
-      <c r="L40" s="22" t="n"/>
+      <c r="K40" s="97" t="n"/>
+      <c r="L40" s="99" t="n"/>
     </row>
     <row r="41" ht="16.5" customHeight="1" s="27">
       <c r="A41" s="77" t="inlineStr">
@@ -2076,24 +2131,24 @@
         </is>
       </c>
       <c r="B43" s="18" t="n"/>
-      <c r="C43" s="19" t="n"/>
-      <c r="D43" s="18" t="n"/>
+      <c r="C43" s="106" t="n"/>
+      <c r="D43" s="108" t="n"/>
       <c r="E43" s="82" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F43" s="18" t="n"/>
-      <c r="G43" s="19" t="n"/>
-      <c r="H43" s="18" t="n"/>
+      <c r="G43" s="106" t="n"/>
+      <c r="H43" s="108" t="n"/>
       <c r="I43" s="82" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="J43" s="18" t="n"/>
-      <c r="K43" s="19" t="n"/>
-      <c r="L43" s="18" t="n"/>
+      <c r="K43" s="106" t="n"/>
+      <c r="L43" s="108" t="n"/>
     </row>
     <row r="44" ht="21" customHeight="1" s="27">
       <c r="A44" s="82" t="inlineStr">
@@ -2102,24 +2157,24 @@
         </is>
       </c>
       <c r="B44" s="18" t="n"/>
-      <c r="C44" s="19" t="n"/>
-      <c r="D44" s="18" t="n"/>
+      <c r="C44" s="106" t="n"/>
+      <c r="D44" s="108" t="n"/>
       <c r="E44" s="82" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="F44" s="18" t="n"/>
-      <c r="G44" s="19" t="n"/>
-      <c r="H44" s="18" t="n"/>
+      <c r="G44" s="106" t="n"/>
+      <c r="H44" s="108" t="n"/>
       <c r="I44" s="82" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="J44" s="18" t="n"/>
-      <c r="K44" s="19" t="n"/>
-      <c r="L44" s="18" t="n"/>
+      <c r="K44" s="106" t="n"/>
+      <c r="L44" s="108" t="n"/>
     </row>
     <row r="45" ht="21" customHeight="1" s="27">
       <c r="A45" s="82" t="inlineStr">
@@ -2128,24 +2183,24 @@
         </is>
       </c>
       <c r="B45" s="18" t="n"/>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="18" t="n"/>
+      <c r="C45" s="106" t="n"/>
+      <c r="D45" s="108" t="n"/>
       <c r="E45" s="82" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="F45" s="18" t="n"/>
-      <c r="G45" s="19" t="n"/>
-      <c r="H45" s="18" t="n"/>
+      <c r="G45" s="106" t="n"/>
+      <c r="H45" s="108" t="n"/>
       <c r="I45" s="82" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="J45" s="18" t="n"/>
-      <c r="K45" s="19" t="n"/>
-      <c r="L45" s="18" t="n"/>
+      <c r="K45" s="106" t="n"/>
+      <c r="L45" s="108" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -2159,6 +2214,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="126">
     <mergeCell ref="G38:I38"/>
     <mergeCell ref="C23:L23"/>
